--- a/extenbooks/ES1302.xlsx
+++ b/extenbooks/ES1302.xlsx
@@ -921,11 +921,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1302 — NSW/EC Extended (Moos 2017) — PENDING</t>
+          <t># ES1302 — Moos NSW/EC Extended</t>
         </is>
       </c>
     </row>
@@ -1097,87 +1097,43 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Moos NSW1 / Moos's own compensation column. 54 rows. Same period, slightly larger swings than ES1301 due to compensation &lt; GDP. Range [-2.65%, +12.70%].</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>needs EC</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Moos / compensation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1302.xlsx
+++ b/extenbooks/ES1302.xlsx
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 4</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1959–2024</t>
+          <t>1959-2012</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1074,54 +1074,63 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1302-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Moos 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1302 — Moos NSW/EC Extended</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1302 — Moos NSW/EC Extended</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Moos NSW1 / Moos's own compensation column. 54 rows. Same period, slightly larger swings than ES1301 due to compensation &lt; GDP. Range [-2.65%, +12.70%].</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Moos NSW1 / Moos's own compensation column. 54 rows. Same period, slightly larger swings than ES1301 due to compensation &lt; GDP. Range [-2.65%, +12.70%].</t>
         </is>
       </c>
     </row>
@@ -1132,6 +1141,18 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1148,10 +1169,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1176,196 +1197,228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ES1302 expresses Moos (2017)'s extended NSW series as a ratio to total employee compensation (EC), rather than GDP (ES1301). This matches Shaikh &amp; Tonak (2002)'s primary normalization (ES1202). Moos primarily reports NSW/GDP (her Figure 1-2) but also presents NSW/EC in Figure 2 (1959-2012). The switch from GDP to EC as denominator amplifies the ratio since EC &lt; GDP; the post-2001 peak is 16.1% of EC in 2010 vs 8.6% of GDP (from Table 2 summary statistics).</t>
+          <t>As a ratio of employee compensation, NSW varies from -2.2% to 16.1% (2010 peak).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 pp.4-5, Table 2; full_transcription.md Section 3 and Figure 2 reference; DECISION_LOG.md DEC-013</t>
+          <t>Moos 2017, Extended Data Series, p.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEC-013 (2026-05-06): Standard Shaikh-Tonak/Moos formula is NSW = E1 - T1 - T2*LS (E2 excluded). With this formula, ST2 P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013 vs Moos published 0.011. The same E2 exclusion applies to ES1302 (NSW/EC). Mean NSW/EC for overlap period from ST2 is correspondingly higher than NSW/GDP due to EC &lt; GDP. V11 benchmark range [0.008, 0.018] applies to the NSW/GDP ratio (ES1301); ES1302 NSW/EC expected to be roughly 1.5-2x higher given EC/GDP ratio historically ~0.55-0.65.</t>
+          <t>In Figure 2, we can see that after 1970, the NSW as a ratio of employee compensation was positive. It is compelling that U.S. fiscal policy appears to be more redistributive towards labor during the neoliberal era, especially in the 21st century.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-013</t>
+          <t>Moos 2017, Section 4, p.6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moos Table 2 summary statistics for full 1959-2012 dataset: NSW/EC ranges from -2.2% (minimum) to 16.1% (maximum, at 2010 peak). The post-2001 structural break is equally pronounced in NSW/EC as in NSW/GDP. Figure 2 in Moos shows that after 1970, NSW/EC was positive, and after 2002 it reached historically unprecedented positive levels. The pattern is qualitatively identical to NSW/GDP but with amplified magnitudes.</t>
+          <t>Shaikh and Tonak (2000) considers the net social wage/ employee compensation. This paper mainly uses the NSW/GDP ratio, which is constructed using the same methodology and can be found in Shaikh (2003).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 Table 2; Section 4 p.6 Figure 2 reference; full_transcription.md Section 3 Extended Net Social Wage Data Series</t>
+          <t>Moos 2017, Note 6 to Section 3, p.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>overlap_comparison</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>For the 1959-1997 overlap period, Shaikh &amp; Tonak (2002) show NSW/EC averaging 0.6% of EC (effectively zero, Figure 29.3 in ST_2002). Moos's replicated series shows NSW/EC is positive for more years in the overlap, consistent with her finding of ~1.1 pp higher NSW/GDP mean. The slight upward shift is attributed to post-1999 NIPA revisions, not methodological differences. The qualitative phase pattern (negative in boom, positive in crisis, near-zero in Clinton era) is preserved.</t>
+          <t>ES1302 expresses Moos (2017)'s extended NSW series as a ratio to total employee compensation (EC), rather than GDP (ES1301). This matches Shaikh &amp; Tonak (2002)'s primary normalization (ES1202). Moos primarily reports NSW/GDP (her Figure 1-2) but also presents NSW/EC in Figure 2 (1959-2012). The switch from GDP to EC as denominator amplifies the ratio since EC &lt; GDP; the post-2001 peak is 16.1% of EC in 2010 vs 8.6% of GDP (from Table 2 summary statistics).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 p.4; full_transcription.md Section 3; ST_2002 p.253</t>
+          <t>Moos_2017, Section 3 pp.4-5, Table 2; full_transcription.md Section 3 and Figure 2 reference; [internal-decision-log] [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>decision_reference</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ES1302 = NSW / EC, where NSW = E1 - T1 - T2*LS (per DEC-013 E2 excluded). EC = total employee compensation from BEA NIPA Table 2.1 (wages + salaries + employer social insurance contributions + other labor income). Labor share LS = wages and salaries / total personal income (secularly declining from ~0.73 in 1960s to ~0.62 by 2010s). Robustness check with Mohun (2016) income share (declining from 0.70 to ~0.45) produces nearly identical NSW/EC path.</t>
+          <t>[internal-decision-record] (2026-05-06): Standard Shaikh-Tonak/Moos formula is NSW = E1 - T1 - T2*LS (E2 excluded). With this formula, ST2 P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013 vs Moos published 0.011. The same E2 exclusion applies to ES1302 (NSW/EC). Mean NSW/EC for overlap period from ST2 is correspondingly higher than NSW/GDP due to EC &lt; GDP. V11 benchmark range [0.008, 0.018] applies to the NSW/GDP ratio (ES1301); ES1302 NSW/EC expected to be roughly 1.5-2x higher given EC/GDP ratio historically ~0.55-0.65.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 2 pp.3-4, Section 4.3 pp.20-23; full_transcription.md Sections 2 and 4.3</t>
+          <t>[internal-decision-log] [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cyclical_driver</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Moos confirms Shaikh &amp; Tonak's finding that unemployment drives NSW variations but extends the analysis: in 1983 and 2010, official unemployment was identical at 9.6%, yet NSW/GDP was 2.1% in 1983 and 8.6% in 2010 (Table 3). The difference is unemployment intensity — product of unemployment rate and duration index. 1983 intensity=18.95%; 2010 intensity=31.46% (66% higher). Long-term unemployment means extended benefit collection. This explains the unprecedented post-2007 NSW/EC without requiring a structural change in benefit generosity.</t>
+          <t>Moos Table 2 summary statistics for full 1959-2012 dataset: NSW/EC ranges from -2.2% (minimum) to 16.1% (maximum, at 2010 peak). The post-2001 structural break is equally pronounced in NSW/EC as in NSW/GDP. Figure 2 in Moos shows that after 1970, NSW/EC was positive, and after 2002 it reached historically unprecedented positive levels. The pattern is qualitatively identical to NSW/GDP but with amplified magnitudes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 4.2.1 pp.17-19; full_transcription.md Table 3 and Section 4.2.1</t>
+          <t>Moos_2017, Section 3 Table 2; Section 4 p.6 Figure 2 reference; full_transcription.md Section 3 Extended Net Social Wage Data Series</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>overlap_comparison</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC from BEA NIPA. Period 1959-2012. Moos uses post-1999 comprehensive NIPA revision. Labor share secular decline documented: high of 0.73 to low of 0.62 over period. EC/GDP ratio declines correspondingly in neoliberal era. Nominal NSW ranges from -$13.18bn to $1,288bn (2010). In real 2010 dollars, ranges -$76.48bn to $1,288bn.</t>
+          <t>For the 1959-1997 overlap period, Shaikh &amp; Tonak (2002) show NSW/EC averaging 0.6% of EC (effectively zero, Figure 29.3 in ST_2002). Moos's replicated series shows NSW/EC is positive for more years in the overlap, consistent with her finding of ~1.1 pp higher NSW/GDP mean. The slight upward shift is attributed to post-1999 NIPA revisions, not methodological differences. The qualitative phase pattern (negative in boom, positive in crisis, near-zero in Clinton era) is preserved.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 Table 2; Section 4.3 p.21; full_transcription.md Sections 3 and 4.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Moos_2017, Section 3 p.4; full_transcription.md Section 3; ST_2002 p.253</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ES1302 = NSW / EC, where NSW = E1 - T1 - T2*LS (per [internal-decision-record] E2 excluded). EC = total employee compensation from BEA NIPA Table 2.1 (wages + salaries + employer social insurance contributions + other labor income). Labor share LS = wages and salaries / total personal income (secularly declining from ~0.73 in 1960s to ~0.62 by 2010s). Robustness check with Mohun (2016) income share (declining from 0.70 to ~0.45) produces nearly identical NSW/EC path.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 2 pp.3-4, Section 4.3 pp.20-23; full_transcription.md Sections 2 and 4.3</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>cyclical_driver</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NSW/EC extended to 2012 by Moos (2017), using same formula as ES1301 but normalized by employee compensation rather than GDP. Period 1959-2012. EC &lt; GDP so NSW/EC magnitudes are larger; post-2001 peak is 16.1% of EC vs 8.6% of GDP. E2 excluded per DEC-013. Direct comparator to ES1202 (ST 2002 NSW/EC).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
+          <t>Moos confirms Shaikh &amp; Tonak's finding that unemployment drives NSW variations but extends the analysis: in 1983 and 2010, official unemployment was identical at 9.6%, yet NSW/GDP was 2.1% in 1983 and 8.6% in 2010 (Table 3). The difference is unemployment intensity — product of unemployment rate and duration index. 1983 intensity=18.95%; 2010 intensity=31.46% (66% higher). Long-term unemployment means extended benefit collection. This explains the unprecedented post-2007 NSW/EC without requiring a structural change in benefit generosity.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 4.2.1 pp.17-19; full_transcription.md Table 3 and Section 4.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EC from BEA NIPA. Period 1959-2012. Moos uses post-1999 comprehensive NIPA revision. Labor share secular decline documented: high of 0.73 to low of 0.62 over period. EC/GDP ratio declines correspondingly in neoliberal era. Nominal NSW ranges from -$13.18bn to $1,288bn (2010). In real 2010 dollars, ranges -$76.48bn to $1,288bn.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 3 Table 2; Section 4.3 p.21; full_transcription.md Sections 3 and 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NIPA vintage difference between Moos (~2015 pull) and ST2 (2026 pull) affects historical EC values</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EC/GDP ratio declining in neoliberal era means normalization choice matters more for post-2001 period</t>
-        </is>
-      </c>
+          <t>As a ratio of employee compensation, NSW varies from -2.2% to 16.1% (2010 peak).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>E2 excluded from NSW per DEC-013; E2 data available for sensitivity analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
+          <t>In Figure 2, we can see that after 1970, the NSW as a ratio of employee compensation was positive. It is compelling that U.S. fiscal policy appears to be more redistributive towards labor during the neoliberal era, especially in the 21st century.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shaikh and Tonak (2000) considers the net social wage/ employee compensation. This paper mainly uses the NSW/GDP ratio, which is constructed using the same methodology and can be found in Shaikh (2003).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1301</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ES1304</t>
-        </is>
-      </c>
-    </row>
+          <t>NSW/EC extended to 2012 by Moos (2017), using same formula as ES1301 but normalized by employee compensation rather than GDP. Period 1959-2012. EC &lt; GDP so NSW/EC magnitudes are larger; post-2001 peak is 16.1% of EC vs 8.6% of GDP. E2 excluded per [internal-decision-record]. Direct comparator to ES1202 (ST 2002 NSW/EC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ES1305</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1426,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ES1202</t>
+          <t>NIPA vintage difference between Moos (~2015 pull) and ST2 (2026 pull) affects historical EC values</t>
         </is>
       </c>
     </row>
@@ -1381,49 +1434,105 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S607</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+          <t>EC/GDP ratio declining in neoliberal era means normalization choice matters more for post-2001 period</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>E2 excluded from NSW per [internal-decision-record]; E2 data available for sensitivity analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES1301</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES1304</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES1305</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES1202</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Moos, Katherine A. 2017. 'Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century.' Working Paper No. 2017-18, Department of Economics, University of Massachusetts Amherst. September 18, 2017.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ST_2002</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism. M.E. Sharpe, Armonk. pp. 247-265.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. Survey of Current Business, various years.</t>
         </is>
@@ -1440,7 +1549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1511,7 +1620,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1641,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"2010": 0.161}</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1665,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
